--- a/data/trans_orig/IP12_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP12_2023-Edad-trans_orig.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables originales" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2023" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -504,7 +504,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q19"/>
+  <dimension ref="A1:W24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -524,12 +524,18 @@
     <col width="14" customWidth="1" min="15" max="15"/>
     <col width="14" customWidth="1" min="16" max="16"/>
     <col width="14" customWidth="1" min="17" max="17"/>
+    <col width="14" customWidth="1" min="18" max="18"/>
+    <col width="14" customWidth="1" min="19" max="19"/>
+    <col width="14" customWidth="1" min="20" max="20"/>
+    <col width="14" customWidth="1" min="21" max="21"/>
+    <col width="14" customWidth="1" min="22" max="22"/>
+    <col width="14" customWidth="1" min="23" max="23"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si en las últimas 2 semanas limitaron su actividad por dolores o síntomas en 2023 (Tasa respuesta: 99,95%)</t>
+          <t>Menores según si en las últimas 2 semanas limitaron su actividad por dolores o síntomas en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -542,24 +548,30 @@
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="n"/>
-      <c r="H1" s="3" t="inlineStr">
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="inlineStr">
         <is>
           <t>Niño</t>
         </is>
       </c>
-      <c r="I1" s="3" t="n"/>
-      <c r="J1" s="3" t="n"/>
       <c r="K1" s="3" t="n"/>
       <c r="L1" s="3" t="n"/>
-      <c r="M1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
+      <c r="M1" s="3" t="n"/>
       <c r="N1" s="3" t="n"/>
       <c r="O1" s="3" t="n"/>
       <c r="P1" s="3" t="n"/>
-      <c r="Q1" s="3" t="n"/>
+      <c r="Q1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="R1" s="3" t="n"/>
+      <c r="S1" s="3" t="n"/>
+      <c r="T1" s="3" t="n"/>
+      <c r="U1" s="3" t="n"/>
+      <c r="V1" s="3" t="n"/>
+      <c r="W1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n"/>
@@ -576,65 +588,95 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
+          <t>N (lím inf IC)</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>N (lím sup IC)</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
           <t>Estimación puntual</t>
         </is>
       </c>
-      <c r="F2" s="3" t="inlineStr">
+      <c r="H2" s="3" t="inlineStr">
         <is>
           <t>lím inf IC</t>
         </is>
       </c>
-      <c r="G2" s="3" t="inlineStr">
+      <c r="I2" s="3" t="inlineStr">
         <is>
           <t>lím sup IC</t>
         </is>
       </c>
-      <c r="H2" s="3" t="inlineStr">
+      <c r="J2" s="3" t="inlineStr">
         <is>
           <t>n (muestra)</t>
         </is>
       </c>
-      <c r="I2" s="3" t="inlineStr">
+      <c r="K2" s="3" t="inlineStr">
         <is>
           <t>N (estimada)</t>
         </is>
       </c>
-      <c r="J2" s="3" t="inlineStr">
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>N (lím inf IC)</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>N (lím sup IC)</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
         <is>
           <t>Estimación puntual</t>
         </is>
       </c>
-      <c r="K2" s="3" t="inlineStr">
+      <c r="O2" s="3" t="inlineStr">
         <is>
           <t>lím inf IC</t>
         </is>
       </c>
-      <c r="L2" s="3" t="inlineStr">
+      <c r="P2" s="3" t="inlineStr">
         <is>
           <t>lím sup IC</t>
         </is>
       </c>
-      <c r="M2" s="3" t="inlineStr">
+      <c r="Q2" s="3" t="inlineStr">
         <is>
           <t>n (muestra)</t>
         </is>
       </c>
-      <c r="N2" s="3" t="inlineStr">
+      <c r="R2" s="3" t="inlineStr">
         <is>
           <t>N (estimada)</t>
         </is>
       </c>
-      <c r="O2" s="3" t="inlineStr">
+      <c r="S2" s="3" t="inlineStr">
+        <is>
+          <t>N (lím inf IC)</t>
+        </is>
+      </c>
+      <c r="T2" s="3" t="inlineStr">
+        <is>
+          <t>N (lím sup IC)</t>
+        </is>
+      </c>
+      <c r="U2" s="3" t="inlineStr">
         <is>
           <t>Estimación puntual</t>
         </is>
       </c>
-      <c r="P2" s="3" t="inlineStr">
+      <c r="V2" s="3" t="inlineStr">
         <is>
           <t>lím inf IC</t>
         </is>
       </c>
-      <c r="Q2" s="3" t="inlineStr">
+      <c r="W2" s="3" t="inlineStr">
         <is>
           <t>lím sup IC</t>
         </is>
@@ -658,6 +700,12 @@
       <c r="O3" s="2" t="n"/>
       <c r="P3" s="2" t="n"/>
       <c r="Q3" s="2" t="n"/>
+      <c r="R3" s="2" t="n"/>
+      <c r="S3" s="2" t="n"/>
+      <c r="T3" s="2" t="n"/>
+      <c r="U3" s="2" t="n"/>
+      <c r="V3" s="2" t="n"/>
+      <c r="W3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -667,70 +715,112 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="D4" s="2" t="n">
-        <v>4575</v>
+          <t>Sí, por algún síntoma</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>4184</t>
+        </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>2013</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>7526</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>14,43%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="I4" s="2" t="n">
-        <v>5544</v>
+          <t>7,28%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>3,5%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>13,09%</t>
+        </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>5544</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>2799</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>10233</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
           <t>9,02%</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>4,54%</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>16,49%</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="N4" s="2" t="n">
-        <v>10119</v>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>16,65%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
-          <t>13,72%</t>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>9728</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>6031</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>15701</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>8,18%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
+          <t>5,07%</t>
+        </is>
+      </c>
+      <c r="W4" s="2" t="inlineStr">
+        <is>
+          <t>13,2%</t>
         </is>
       </c>
     </row>
@@ -738,70 +828,112 @@
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="n">
-        <v>99</v>
-      </c>
-      <c r="D5" s="2" t="n">
-        <v>52936</v>
+          <t>Sí, por algún dolor</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>391</t>
+        </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>92,04%</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>85,57%</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>95,86%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="n">
-        <v>106</v>
-      </c>
-      <c r="I5" s="2" t="n">
-        <v>55900</v>
+          <t>0,68%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>3,51%</t>
+        </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>90,98%</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>83,51%</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>95,46%</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="n">
-        <v>205</v>
-      </c>
-      <c r="N5" s="2" t="n">
-        <v>108836</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>91,49%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>86,28%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
-          <t>94,73%</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>391</t>
+        </is>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>1956</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
+          <t>0,33%</t>
+        </is>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="W5" s="2" t="inlineStr">
+        <is>
+          <t>1,64%</t>
         </is>
       </c>
     </row>
@@ -809,216 +941,342 @@
       <c r="A6" s="1" t="n"/>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="n">
-        <v>109</v>
-      </c>
-      <c r="D6" s="2" t="n">
-        <v>57511</v>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>52936</t>
+        </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>49349</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>55206</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="n">
-        <v>116</v>
-      </c>
-      <c r="I6" s="2" t="n">
-        <v>61444</v>
+          <t>92,04%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>85,81%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>95,99%</t>
+        </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>106</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>55900</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="n">
-        <v>225</v>
-      </c>
-      <c r="N6" s="2" t="n">
-        <v>118955</v>
+          <t>51211</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>58645</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>90,98%</t>
+        </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>83,35%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>95,44%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>205</t>
+        </is>
+      </c>
+      <c r="R6" s="2" t="inlineStr">
+        <is>
+          <t>108836</t>
+        </is>
+      </c>
+      <c r="S6" s="2" t="inlineStr">
+        <is>
+          <t>103068</t>
+        </is>
+      </c>
+      <c r="T6" s="2" t="inlineStr">
+        <is>
+          <t>112842</t>
+        </is>
+      </c>
+      <c r="U6" s="2" t="inlineStr">
+        <is>
+          <t>91,49%</t>
+        </is>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>86,64%</t>
+        </is>
+      </c>
+      <c r="W6" s="2" t="inlineStr">
+        <is>
+          <t>94,86%</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t>3-7</t>
-        </is>
-      </c>
+      <c r="A7" s="1" t="n"/>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="n">
-        <v>24</v>
-      </c>
-      <c r="D7" s="2" t="n">
-        <v>13265</v>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>57511</t>
+        </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>57511</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>57511</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>12,51%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="n">
-        <v>27</v>
-      </c>
-      <c r="I7" s="2" t="n">
-        <v>16037</v>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>8,78%</t>
+          <t>116</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>61444</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>13,64%</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="n">
-        <v>51</v>
-      </c>
-      <c r="N7" s="2" t="n">
-        <v>29303</v>
+          <t>61444</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>61444</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
-          <t>11,14%</t>
+          <t>225</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>118955</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>118955</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>118955</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="W7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n"/>
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>3-7</t>
+        </is>
+      </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="n">
-        <v>234</v>
-      </c>
-      <c r="D8" s="2" t="n">
-        <v>146034</v>
+          <t>Sí, por algún síntoma</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>8820</t>
+        </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>91,67%</t>
+          <t>5289</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>87,49%</t>
+          <t>13820</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>94,6%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="n">
-        <v>249</v>
-      </c>
-      <c r="I8" s="2" t="n">
-        <v>166517</v>
+          <t>5,54%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>3,32%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>8,68%</t>
+        </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>91,22%</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>86,36%</t>
+          <t>12626</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>93,99%</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="n">
-        <v>483</v>
-      </c>
-      <c r="N8" s="2" t="n">
-        <v>312550</v>
+          <t>7688</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>19211</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>6,92%</t>
+        </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>91,43%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>88,86%</t>
+          <t>10,52%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
-          <t>93,57%</t>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>21446</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>14785</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>29649</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>6,27%</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>4,33%</t>
+        </is>
+      </c>
+      <c r="W8" s="2" t="inlineStr">
+        <is>
+          <t>8,67%</t>
         </is>
       </c>
     </row>
@@ -1026,145 +1284,225 @@
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="n">
-        <v>258</v>
-      </c>
-      <c r="D9" s="2" t="n">
-        <v>159299</v>
+          <t>Sí, por algún dolor</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>4445</t>
+        </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>1925</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>8421</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="n">
-        <v>276</v>
-      </c>
-      <c r="I9" s="2" t="n">
-        <v>182554</v>
+          <t>2,79%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>1,21%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>5,29%</t>
+        </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>7</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>3411</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="n">
-        <v>534</v>
-      </c>
-      <c r="N9" s="2" t="n">
-        <v>341853</v>
+          <t>1274</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>7976</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>1,87%</t>
+        </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="R9" s="2" t="inlineStr">
+        <is>
+          <t>7857</t>
+        </is>
+      </c>
+      <c r="S9" s="2" t="inlineStr">
+        <is>
+          <t>4277</t>
+        </is>
+      </c>
+      <c r="T9" s="2" t="inlineStr">
+        <is>
+          <t>13173</t>
+        </is>
+      </c>
+      <c r="U9" s="2" t="inlineStr">
+        <is>
+          <t>2,3%</t>
+        </is>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>1,25%</t>
+        </is>
+      </c>
+      <c r="W9" s="2" t="inlineStr">
+        <is>
+          <t>3,85%</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>8-11</t>
-        </is>
-      </c>
+      <c r="A10" s="1" t="n"/>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="D10" s="2" t="n">
-        <v>14863</v>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>234</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>146034</t>
+        </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>139881</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>150535</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>12,66%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="I10" s="2" t="n">
-        <v>14875</v>
+          <t>91,67%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>87,81%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>94,5%</t>
+        </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>249</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>166517</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="n">
-        <v>39</v>
-      </c>
-      <c r="N10" s="2" t="n">
-        <v>29738</v>
+          <t>159564</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>171952</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>91,22%</t>
+        </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>87,41%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>94,19%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
-          <t>10,46%</t>
+          <t>483</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>312550</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>303753</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>320607</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>91,43%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>88,85%</t>
+        </is>
+      </c>
+      <c r="W10" s="2" t="inlineStr">
+        <is>
+          <t>93,78%</t>
         </is>
       </c>
     </row>
@@ -1172,216 +1510,342 @@
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="n">
-        <v>212</v>
-      </c>
-      <c r="D11" s="2" t="n">
-        <v>158209</v>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>258</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>159299</t>
+        </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>91,41%</t>
+          <t>159299</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>87,34%</t>
+          <t>159299</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>94,47%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="n">
-        <v>225</v>
-      </c>
-      <c r="I11" s="2" t="n">
-        <v>197615</v>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>93,0%</t>
+          <t>276</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>89,61%</t>
+          <t>182554</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>95,71%</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="n">
-        <v>437</v>
-      </c>
-      <c r="N11" s="2" t="n">
-        <v>355825</v>
+          <t>182554</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>182554</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>92,29%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>89,54%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
-          <t>94,45%</t>
+          <t>534</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>341853</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>341853</t>
+        </is>
+      </c>
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t>341853</t>
+        </is>
+      </c>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="W11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n"/>
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>8-11</t>
+        </is>
+      </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="n">
-        <v>233</v>
-      </c>
-      <c r="D12" s="2" t="n">
-        <v>173072</v>
+          <t>Sí, por algún síntoma</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>9302</t>
+        </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>4906</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>15205</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="n">
-        <v>243</v>
-      </c>
-      <c r="I12" s="2" t="n">
-        <v>212490</v>
+          <t>5,37%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>2,83%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>8,79%</t>
+        </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>11</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>9230</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="n">
-        <v>476</v>
-      </c>
-      <c r="N12" s="2" t="n">
-        <v>385563</v>
+          <t>4398</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>15795</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>4,34%</t>
+        </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="R12" s="2" t="inlineStr">
+        <is>
+          <t>18532</t>
+        </is>
+      </c>
+      <c r="S12" s="2" t="inlineStr">
+        <is>
+          <t>11854</t>
+        </is>
+      </c>
+      <c r="T12" s="2" t="inlineStr">
+        <is>
+          <t>26200</t>
+        </is>
+      </c>
+      <c r="U12" s="2" t="inlineStr">
+        <is>
+          <t>4,81%</t>
+        </is>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>3,07%</t>
+        </is>
+      </c>
+      <c r="W12" s="2" t="inlineStr">
+        <is>
+          <t>6,8%</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>12-15</t>
-        </is>
-      </c>
+      <c r="A13" s="1" t="n"/>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="n">
-        <v>22</v>
-      </c>
-      <c r="D13" s="2" t="n">
-        <v>14568</v>
+          <t>Sí, por algún dolor</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>5561</t>
+        </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>2377</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>10895</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="n">
-        <v>25</v>
-      </c>
-      <c r="I13" s="2" t="n">
-        <v>22647</v>
+          <t>3,21%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>1,37%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>6,3%</t>
+        </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>7</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>5645</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>11,31%</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="n">
-        <v>47</v>
-      </c>
-      <c r="N13" s="2" t="n">
-        <v>37215</v>
+          <t>2266</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>10888</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>2,66%</t>
+        </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>11206</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>6318</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>17549</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>2,91%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>1,64%</t>
+        </is>
+      </c>
+      <c r="W13" s="2" t="inlineStr">
+        <is>
+          <t>4,55%</t>
         </is>
       </c>
     </row>
@@ -1392,67 +1856,109 @@
           <t>No</t>
         </is>
       </c>
-      <c r="C14" s="2" t="n">
-        <v>320</v>
-      </c>
-      <c r="D14" s="2" t="n">
-        <v>260890</v>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>212</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>158209</t>
+        </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>94,71%</t>
+          <t>151344</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>92,1%</t>
+          <t>163998</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>96,89%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="n">
-        <v>317</v>
-      </c>
-      <c r="I14" s="2" t="n">
-        <v>282836</v>
+          <t>91,41%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>87,45%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>94,76%</t>
+        </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>92,59%</t>
+          <t>225</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>88,69%</t>
+          <t>197615</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>95,12%</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="n">
-        <v>637</v>
-      </c>
-      <c r="N14" s="2" t="n">
-        <v>543725</v>
+          <t>190366</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>203527</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>93,0%</t>
+        </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,59%</t>
+          <t>89,59%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>91,47%</t>
+          <t>95,78%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
-          <t>95,42%</t>
+          <t>437</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>355825</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>344400</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>363742</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>92,29%</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>89,32%</t>
+        </is>
+      </c>
+      <c r="W14" s="2" t="inlineStr">
+        <is>
+          <t>94,34%</t>
         </is>
       </c>
     </row>
@@ -1463,20 +1969,24 @@
           <t>Total</t>
         </is>
       </c>
-      <c r="C15" s="2" t="n">
-        <v>342</v>
-      </c>
-      <c r="D15" s="2" t="n">
-        <v>275458</v>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>233</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>173072</t>
+        </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>173072</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>173072</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1484,32 +1994,40 @@
           <t>100%</t>
         </is>
       </c>
-      <c r="H15" s="2" t="n">
-        <v>342</v>
-      </c>
-      <c r="I15" s="2" t="n">
-        <v>305483</v>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>243</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>212490</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="n">
-        <v>684</v>
-      </c>
-      <c r="N15" s="2" t="n">
-        <v>580940</v>
+          <t>212490</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>212490</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
@@ -1522,6 +2040,36 @@
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
+        <is>
+          <t>476</t>
+        </is>
+      </c>
+      <c r="R15" s="2" t="inlineStr">
+        <is>
+          <t>385563</t>
+        </is>
+      </c>
+      <c r="S15" s="2" t="inlineStr">
+        <is>
+          <t>385563</t>
+        </is>
+      </c>
+      <c r="T15" s="2" t="inlineStr">
+        <is>
+          <t>385563</t>
+        </is>
+      </c>
+      <c r="U15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="W15" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -1530,75 +2078,117 @@
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>12-15</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="n">
-        <v>77</v>
-      </c>
-      <c r="D16" s="2" t="n">
-        <v>47272</v>
+          <t>Sí, por algún síntoma</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>10244</t>
+        </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>5731</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>16977</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>8,98%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="n">
-        <v>80</v>
-      </c>
-      <c r="I16" s="2" t="n">
-        <v>59103</v>
+          <t>3,72%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>2,08%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>6,16%</t>
+        </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>18135</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>9,74%</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="n">
-        <v>157</v>
-      </c>
-      <c r="N16" s="2" t="n">
-        <v>106375</v>
+          <t>10968</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>29845</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>5,94%</t>
+        </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>9,77%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
         <is>
-          <t>8,73%</t>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>28379</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>19800</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>39621</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>4,89%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>3,41%</t>
+        </is>
+      </c>
+      <c r="W16" s="2" t="inlineStr">
+        <is>
+          <t>6,82%</t>
         </is>
       </c>
     </row>
@@ -1606,70 +2196,112 @@
       <c r="A17" s="1" t="n"/>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="n">
-        <v>865</v>
-      </c>
-      <c r="D17" s="2" t="n">
-        <v>618068</v>
+          <t>Sí, por algún dolor</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>4324</t>
+        </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>92,9%</t>
+          <t>1688</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>91,02%</t>
+          <t>9573</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>94,48%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="n">
-        <v>897</v>
-      </c>
-      <c r="I17" s="2" t="n">
-        <v>702869</v>
+          <t>1,57%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>0,61%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>3,48%</t>
+        </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>92,24%</t>
+          <t>5</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>90,26%</t>
+          <t>4512</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>93,92%</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="n">
-        <v>1762</v>
-      </c>
-      <c r="N17" s="2" t="n">
-        <v>1320937</v>
+          <t>1675</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>10468</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>1,48%</t>
+        </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>92,55%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>91,27%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
-          <t>93,75%</t>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>8836</t>
+        </is>
+      </c>
+      <c r="S17" s="2" t="inlineStr">
+        <is>
+          <t>4656</t>
+        </is>
+      </c>
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t>15387</t>
+        </is>
+      </c>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>1,52%</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>0,8%</t>
+        </is>
+      </c>
+      <c r="W17" s="2" t="inlineStr">
+        <is>
+          <t>2,65%</t>
         </is>
       </c>
     </row>
@@ -1677,75 +2309,686 @@
       <c r="A18" s="1" t="n"/>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="n">
-        <v>942</v>
-      </c>
-      <c r="D18" s="2" t="n">
-        <v>665340</v>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>320</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>260890</t>
+        </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>253860</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>266519</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="n">
-        <v>977</v>
-      </c>
-      <c r="I18" s="2" t="n">
-        <v>761972</v>
+          <t>94,71%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>92,16%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>96,75%</t>
+        </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>317</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>282836</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="n">
-        <v>1919</v>
-      </c>
-      <c r="N18" s="2" t="n">
-        <v>1427312</v>
+          <t>271097</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>291103</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>92,59%</t>
+        </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>88,74%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>95,29%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>637</t>
+        </is>
+      </c>
+      <c r="R18" s="2" t="inlineStr">
+        <is>
+          <t>543725</t>
+        </is>
+      </c>
+      <c r="S18" s="2" t="inlineStr">
+        <is>
+          <t>531941</t>
+        </is>
+      </c>
+      <c r="T18" s="2" t="inlineStr">
+        <is>
+          <t>553901</t>
+        </is>
+      </c>
+      <c r="U18" s="2" t="inlineStr">
+        <is>
+          <t>93,59%</t>
+        </is>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
+          <t>91,57%</t>
+        </is>
+      </c>
+      <c r="W18" s="2" t="inlineStr">
+        <is>
+          <t>95,35%</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
+      <c r="A19" s="1" t="n"/>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>342</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>275458</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>275458</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>275458</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>342</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>305483</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>305483</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>305483</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>684</t>
+        </is>
+      </c>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
+          <t>580940</t>
+        </is>
+      </c>
+      <c r="S19" s="2" t="inlineStr">
+        <is>
+          <t>580940</t>
+        </is>
+      </c>
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>580940</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="W19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>Sí, por algún síntoma</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>32551</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>23273</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>42140</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>4,89%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>3,5%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>6,33%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>45535</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>33747</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>58792</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>5,98%</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>4,43%</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>7,72%</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="R20" s="2" t="inlineStr">
+        <is>
+          <t>78086</t>
+        </is>
+      </c>
+      <c r="S20" s="2" t="inlineStr">
+        <is>
+          <t>63860</t>
+        </is>
+      </c>
+      <c r="T20" s="2" t="inlineStr">
+        <is>
+          <t>95162</t>
+        </is>
+      </c>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
+          <t>5,47%</t>
+        </is>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
+          <t>4,47%</t>
+        </is>
+      </c>
+      <c r="W20" s="2" t="inlineStr">
+        <is>
+          <t>6,67%</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>Sí, por algún dolor</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>14721</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>9220</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>22171</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>2,21%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>1,39%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>3,33%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>13568</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>8264</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>21555</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>1,78%</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>1,08%</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t>2,83%</t>
+        </is>
+      </c>
+      <c r="Q21" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="R21" s="2" t="inlineStr">
+        <is>
+          <t>28290</t>
+        </is>
+      </c>
+      <c r="S21" s="2" t="inlineStr">
+        <is>
+          <t>20251</t>
+        </is>
+      </c>
+      <c r="T21" s="2" t="inlineStr">
+        <is>
+          <t>38405</t>
+        </is>
+      </c>
+      <c r="U21" s="2" t="inlineStr">
+        <is>
+          <t>1,98%</t>
+        </is>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
+        <is>
+          <t>1,42%</t>
+        </is>
+      </c>
+      <c r="W21" s="2" t="inlineStr">
+        <is>
+          <t>2,69%</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="n"/>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>865</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>618068</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>606023</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>629362</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>92,9%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>91,08%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>94,59%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>897</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>702869</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>687116</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>714365</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>92,24%</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>90,18%</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>93,75%</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>1762</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>1320937</t>
+        </is>
+      </c>
+      <c r="S22" s="2" t="inlineStr">
+        <is>
+          <t>1300177</t>
+        </is>
+      </c>
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>1337647</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>92,55%</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
+          <t>91,09%</t>
+        </is>
+      </c>
+      <c r="W22" s="2" t="inlineStr">
+        <is>
+          <t>93,72%</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>942</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>665340</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>665340</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>665340</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>977</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>761972</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>761972</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>761972</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr">
+        <is>
+          <t>1919</t>
+        </is>
+      </c>
+      <c r="R23" s="2" t="inlineStr">
+        <is>
+          <t>1427312</t>
+        </is>
+      </c>
+      <c r="S23" s="2" t="inlineStr">
+        <is>
+          <t>1427312</t>
+        </is>
+      </c>
+      <c r="T23" s="2" t="inlineStr">
+        <is>
+          <t>1427312</t>
+        </is>
+      </c>
+      <c r="U23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="W23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1753,15 +2996,15 @@
     </row>
   </sheetData>
   <mergeCells count="9">
-    <mergeCell ref="A7:A9"/>
-    <mergeCell ref="A4:A6"/>
-    <mergeCell ref="A16:A18"/>
-    <mergeCell ref="A10:A12"/>
-    <mergeCell ref="C1:G1"/>
-    <mergeCell ref="H1:L1"/>
+    <mergeCell ref="J1:P1"/>
+    <mergeCell ref="A4:A7"/>
+    <mergeCell ref="A8:A11"/>
+    <mergeCell ref="A12:A15"/>
+    <mergeCell ref="A20:A23"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="M1:Q1"/>
-    <mergeCell ref="A13:A15"/>
+    <mergeCell ref="Q1:W1"/>
+    <mergeCell ref="C1:I1"/>
+    <mergeCell ref="A16:A19"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/trans_orig/IP12_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP12_2023-Edad-trans_orig.xlsx
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2013</t>
+          <t>1967</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7526</t>
+          <t>7596</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>13,09%</t>
+          <t>13,21%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2799</t>
+          <t>2728</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>10233</t>
+          <t>10147</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>16,65%</t>
+          <t>16,51%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>6031</t>
+          <t>5987</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>15701</t>
+          <t>15025</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>13,2%</t>
+          <t>12,63%</t>
         </is>
       </c>
     </row>
@@ -848,7 +848,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2199</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -863,7 +863,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1956</t>
+          <t>2133</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -933,7 +933,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,79%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>49349</t>
+          <t>49213</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>55206</t>
+          <t>55338</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>85,81%</t>
+          <t>85,57%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>95,99%</t>
+          <t>96,22%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>51211</t>
+          <t>51297</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>58645</t>
+          <t>58716</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>83,35%</t>
+          <t>83,49%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>95,44%</t>
+          <t>95,56%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>103068</t>
+          <t>103561</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>112842</t>
+          <t>112746</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>86,64%</t>
+          <t>87,06%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>94,86%</t>
+          <t>94,78%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>5289</t>
+          <t>5242</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>13820</t>
+          <t>13946</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>8,75%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>7688</t>
+          <t>7805</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>19211</t>
+          <t>19153</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>10,52%</t>
+          <t>10,49%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>14785</t>
+          <t>14974</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>29649</t>
+          <t>29781</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>8,71%</t>
         </is>
       </c>
     </row>
@@ -1299,12 +1299,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1925</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>8421</t>
+          <t>8976</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1314,12 +1314,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1334,12 +1334,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1274</t>
+          <t>1254</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>7976</t>
+          <t>7477</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1349,12 +1349,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1369,12 +1369,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>4277</t>
+          <t>4515</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>13173</t>
+          <t>12677</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1384,12 +1384,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,71%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>139881</t>
+          <t>139520</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>150535</t>
+          <t>150943</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>87,81%</t>
+          <t>87,58%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>94,5%</t>
+          <t>94,75%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>159564</t>
+          <t>159158</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>171952</t>
+          <t>171887</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>87,41%</t>
+          <t>87,18%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>94,19%</t>
+          <t>94,16%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>303753</t>
+          <t>303445</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>320607</t>
+          <t>319677</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>88,85%</t>
+          <t>88,76%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>93,78%</t>
+          <t>93,51%</t>
         </is>
       </c>
     </row>
@@ -1642,12 +1642,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>4906</t>
+          <t>5181</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>15205</t>
+          <t>15590</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1657,12 +1657,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>9,01%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1677,12 +1677,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>4398</t>
+          <t>4913</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>15795</t>
+          <t>15928</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1692,12 +1692,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>7,5%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1712,12 +1712,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>11854</t>
+          <t>12238</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>26200</t>
+          <t>28147</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1727,12 +1727,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>7,3%</t>
         </is>
       </c>
     </row>
@@ -1755,12 +1755,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2377</t>
+          <t>2453</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>10895</t>
+          <t>11115</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1770,12 +1770,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1790,12 +1790,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2266</t>
+          <t>2135</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>10888</t>
+          <t>11085</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1805,12 +1805,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1825,12 +1825,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>6318</t>
+          <t>6380</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>17549</t>
+          <t>18839</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1840,12 +1840,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,89%</t>
         </is>
       </c>
     </row>
@@ -1868,12 +1868,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>151344</t>
+          <t>150109</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>163998</t>
+          <t>163630</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1883,12 +1883,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>87,45%</t>
+          <t>86,73%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,76%</t>
+          <t>94,54%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1903,12 +1903,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>190366</t>
+          <t>189789</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>203527</t>
+          <t>203347</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>89,59%</t>
+          <t>89,32%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,78%</t>
+          <t>95,7%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>344400</t>
+          <t>345589</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>363742</t>
+          <t>364903</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1953,12 +1953,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>89,32%</t>
+          <t>89,63%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,34%</t>
+          <t>94,64%</t>
         </is>
       </c>
     </row>
@@ -2098,12 +2098,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5731</t>
+          <t>5724</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>16977</t>
+          <t>16687</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2118,7 +2118,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>6,06%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2133,12 +2133,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>10968</t>
+          <t>11234</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>29845</t>
+          <t>29162</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2148,12 +2148,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,77%</t>
+          <t>9,55%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2168,12 +2168,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>19800</t>
+          <t>19334</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>39621</t>
+          <t>40701</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2183,12 +2183,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>7,01%</t>
         </is>
       </c>
     </row>
@@ -2211,12 +2211,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1688</t>
+          <t>1627</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>9573</t>
+          <t>9010</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2226,12 +2226,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2246,12 +2246,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1675</t>
+          <t>1548</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>10468</t>
+          <t>10420</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2261,12 +2261,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2281,12 +2281,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>4656</t>
+          <t>4147</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>15387</t>
+          <t>15003</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2296,12 +2296,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,58%</t>
         </is>
       </c>
     </row>
@@ -2324,12 +2324,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>253860</t>
+          <t>253456</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>266519</t>
+          <t>266867</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>92,16%</t>
+          <t>92,01%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>96,75%</t>
+          <t>96,88%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2359,12 +2359,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>271097</t>
+          <t>271137</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>291103</t>
+          <t>290897</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2374,12 +2374,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>88,74%</t>
+          <t>88,76%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>95,29%</t>
+          <t>95,23%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2394,12 +2394,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>531941</t>
+          <t>529510</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>553901</t>
+          <t>554419</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2409,12 +2409,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>91,57%</t>
+          <t>91,15%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>95,35%</t>
+          <t>95,43%</t>
         </is>
       </c>
     </row>
@@ -2554,12 +2554,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>23273</t>
+          <t>24459</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>42140</t>
+          <t>42378</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2569,12 +2569,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2589,12 +2589,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>33747</t>
+          <t>34598</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>58792</t>
+          <t>59646</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2604,12 +2604,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>7,83%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2624,12 +2624,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>63860</t>
+          <t>65252</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>95162</t>
+          <t>95291</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2639,12 +2639,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>6,68%</t>
         </is>
       </c>
     </row>
@@ -2667,12 +2667,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>9220</t>
+          <t>9523</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>22171</t>
+          <t>21824</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2682,12 +2682,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2702,12 +2702,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>8264</t>
+          <t>7886</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>21555</t>
+          <t>21745</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2717,12 +2717,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2737,12 +2737,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>20251</t>
+          <t>20271</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>38405</t>
+          <t>38237</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2757,7 +2757,7 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,68%</t>
         </is>
       </c>
     </row>
@@ -2780,12 +2780,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>606023</t>
+          <t>606801</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>629362</t>
+          <t>628324</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2795,12 +2795,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>91,08%</t>
+          <t>91,2%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>94,59%</t>
+          <t>94,44%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2815,12 +2815,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>687116</t>
+          <t>689239</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>714365</t>
+          <t>716087</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2830,12 +2830,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>90,18%</t>
+          <t>90,45%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>93,75%</t>
+          <t>93,98%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2850,12 +2850,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1300177</t>
+          <t>1301380</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1337647</t>
+          <t>1337289</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2865,12 +2865,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>91,09%</t>
+          <t>91,18%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>93,72%</t>
+          <t>93,69%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP12_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP12_2023-Edad-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,72 +720,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>4489</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>2215</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>8321</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>8,88%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>4,38%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>16,46%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>4184</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>1967</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>7596</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>7,28%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>3,42%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>13,21%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>5544</t>
+          <t>3811</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2728</t>
+          <t>1889</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>10147</t>
+          <t>7163</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>9,02%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>16,51%</t>
+          <t>13,75%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>9728</t>
+          <t>8300</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>5987</t>
+          <t>5305</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>15025</t>
+          <t>13902</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>8,09%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>12,63%</t>
+          <t>13,55%</t>
         </is>
       </c>
     </row>
@@ -833,107 +833,107 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>391</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>340</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>2199</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>0,68%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>1663</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>0,65%</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>3,82%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>3,19%</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>340</t>
+        </is>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>1730</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
+          <t>0,33%</t>
+        </is>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>391</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>2133</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>0,33%</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,69%</t>
         </is>
       </c>
     </row>
@@ -946,72 +946,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>106</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>46048</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>42216</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>48322</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>91,12%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>83,54%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>95,62%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>99</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>52936</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>49213</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>55338</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>92,04%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>85,57%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>96,22%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>106</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>55900</t>
+          <t>47939</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>51297</t>
+          <t>44340</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>58716</t>
+          <t>49939</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>90,98%</t>
+          <t>92,03%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>83,49%</t>
+          <t>85,12%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>95,56%</t>
+          <t>95,87%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>108836</t>
+          <t>93987</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>103561</t>
+          <t>88592</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>112746</t>
+          <t>97276</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>91,49%</t>
+          <t>91,58%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>87,06%</t>
+          <t>86,32%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>94,78%</t>
+          <t>94,79%</t>
         </is>
       </c>
     </row>
@@ -1059,57 +1059,57 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>50537</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>50537</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>50537</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>109</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>57511</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>57511</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>57511</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>116</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>61444</t>
+          <t>52090</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>61444</t>
+          <t>52090</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>61444</t>
+          <t>52090</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1134,17 +1134,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>118955</t>
+          <t>102627</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>118955</t>
+          <t>102627</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>118955</t>
+          <t>102627</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1176,72 +1176,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>10847</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>6529</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>17341</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>6,89%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>4,14%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>11,01%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>8820</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>5242</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>13946</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>5,54%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>3,29%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>8,75%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>12626</t>
+          <t>8092</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>7805</t>
+          <t>4572</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>19153</t>
+          <t>12856</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>10,49%</t>
+          <t>8,83%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>21446</t>
+          <t>18939</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>14974</t>
+          <t>13557</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>29781</t>
+          <t>26269</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>8,71%</t>
+          <t>8,67%</t>
         </is>
       </c>
     </row>
@@ -1289,72 +1289,72 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>3050</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>1250</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>7125</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>1,94%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>0,79%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>4,52%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>4445</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>2021</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>8976</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>2,79%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>1,27%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>5,63%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3411</t>
+          <t>4256</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1254</t>
+          <t>1960</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>7477</t>
+          <t>8551</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>7857</t>
+          <t>7306</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>4515</t>
+          <t>4211</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>12677</t>
+          <t>12308</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>4,06%</t>
         </is>
       </c>
     </row>
@@ -1402,72 +1402,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>249</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>143625</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>135789</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>148106</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>91,18%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>86,2%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>94,02%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>234</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>146034</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>139520</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>150943</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>91,67%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>87,58%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>94,75%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>249</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>166517</t>
+          <t>133170</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>159158</t>
+          <t>127143</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>171887</t>
+          <t>137458</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>91,22%</t>
+          <t>91,51%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>87,18%</t>
+          <t>87,37%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>94,16%</t>
+          <t>94,46%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>312550</t>
+          <t>276794</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>303445</t>
+          <t>268947</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>319677</t>
+          <t>283488</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>91,43%</t>
+          <t>91,34%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>88,76%</t>
+          <t>88,75%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>93,51%</t>
+          <t>93,55%</t>
         </is>
       </c>
     </row>
@@ -1515,57 +1515,57 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>276</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>157522</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>157522</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>157522</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>258</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>159299</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>159299</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>159299</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>276</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>182554</t>
+          <t>145518</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>182554</t>
+          <t>145518</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>182554</t>
+          <t>145518</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1590,17 +1590,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>341853</t>
+          <t>303039</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>341853</t>
+          <t>303039</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>341853</t>
+          <t>303039</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1632,72 +1632,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>8903</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>4665</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>15169</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>4,45%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>2,33%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>7,58%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>9302</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>5181</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>15590</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>5,37%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>2,99%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>9,01%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>9230</t>
+          <t>9496</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>4913</t>
+          <t>5206</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>15928</t>
+          <t>15495</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>8,87%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1707,32 +1707,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>18532</t>
+          <t>18399</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>12238</t>
+          <t>11966</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>28147</t>
+          <t>26596</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>7,1%</t>
         </is>
       </c>
     </row>
@@ -1745,72 +1745,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>5607</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>2473</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>11507</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>2,8%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>1,24%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>5,75%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>5561</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>2453</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>11115</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>3,21%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>1,42%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>6,42%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>5645</t>
+          <t>5534</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2135</t>
+          <t>2372</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>11085</t>
+          <t>11297</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1820,32 +1820,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>11206</t>
+          <t>11141</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>6380</t>
+          <t>6521</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>18839</t>
+          <t>17833</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>4,76%</t>
         </is>
       </c>
     </row>
@@ -1858,72 +1858,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>225</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>185617</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>178471</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>191253</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>92,75%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>89,18%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>95,57%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>212</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>158209</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>150109</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>163630</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>91,41%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>86,73%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>94,54%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>225</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>197615</t>
+          <t>159641</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>189789</t>
+          <t>152120</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>203347</t>
+          <t>165015</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>93,0%</t>
+          <t>91,39%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>89,32%</t>
+          <t>87,09%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,7%</t>
+          <t>94,47%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1933,32 +1933,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>355825</t>
+          <t>345258</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>345589</t>
+          <t>334489</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>364903</t>
+          <t>353456</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>92,29%</t>
+          <t>92,12%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>89,63%</t>
+          <t>89,25%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,64%</t>
+          <t>94,31%</t>
         </is>
       </c>
     </row>
@@ -1971,57 +1971,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>243</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>200126</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>200126</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>200126</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>233</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>173072</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>173072</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>173072</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>243</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>212490</t>
+          <t>174672</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>212490</t>
+          <t>174672</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>212490</t>
+          <t>174672</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2046,17 +2046,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>385563</t>
+          <t>374798</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>385563</t>
+          <t>374798</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>385563</t>
+          <t>374798</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2088,72 +2088,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>18039</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>11098</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>29227</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>6,16%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>3,79%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>9,99%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>10244</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>5724</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>16687</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>3,72%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>2,08%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>6,06%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>18135</t>
+          <t>10591</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>11234</t>
+          <t>6158</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>29162</t>
+          <t>16927</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,55%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2163,32 +2163,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>28379</t>
+          <t>28630</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>19334</t>
+          <t>19715</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>40701</t>
+          <t>40186</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>7,32%</t>
         </is>
       </c>
     </row>
@@ -2201,72 +2201,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>4470</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>1535</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>10401</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>1,53%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>0,52%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>3,55%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>4324</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>1627</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>9010</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>1,57%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>0,59%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>3,27%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>4512</t>
+          <t>4528</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1548</t>
+          <t>1954</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>10420</t>
+          <t>9710</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2276,32 +2276,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>8836</t>
+          <t>8998</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>4147</t>
+          <t>4738</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>15003</t>
+          <t>16179</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,95%</t>
         </is>
       </c>
     </row>
@@ -2314,72 +2314,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>317</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>270136</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>258827</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>277961</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>92,31%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>88,44%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>94,98%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>320</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>260890</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>253456</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>266867</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>94,71%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>92,01%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>96,88%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>317</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>282836</t>
+          <t>241434</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>271137</t>
+          <t>234127</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>290897</t>
+          <t>246502</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>92,59%</t>
+          <t>94,11%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>88,76%</t>
+          <t>91,26%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>95,23%</t>
+          <t>96,08%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2389,32 +2389,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>543725</t>
+          <t>511570</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>529510</t>
+          <t>499752</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>554419</t>
+          <t>521974</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>93,59%</t>
+          <t>93,15%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>91,15%</t>
+          <t>91,0%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>95,43%</t>
+          <t>95,04%</t>
         </is>
       </c>
     </row>
@@ -2432,17 +2432,17 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>275458</t>
+          <t>292645</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>275458</t>
+          <t>292645</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>275458</t>
+          <t>292645</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2467,17 +2467,17 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>305483</t>
+          <t>256553</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>305483</t>
+          <t>256553</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>305483</t>
+          <t>256553</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2502,17 +2502,17 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>580940</t>
+          <t>549198</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>580940</t>
+          <t>549198</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>580940</t>
+          <t>549198</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2544,72 +2544,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>42278</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>31638</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>56786</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>6,03%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>4,51%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>8,1%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>54</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>32551</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>24459</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>42378</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>4,89%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>3,68%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>6,37%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>45535</t>
+          <t>31990</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>34598</t>
+          <t>24045</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>59646</t>
+          <t>41922</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2619,32 +2619,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>78086</t>
+          <t>74268</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>65252</t>
+          <t>61127</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>95291</t>
+          <t>91555</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>6,89%</t>
         </is>
       </c>
     </row>
@@ -2657,72 +2657,72 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>13127</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>7972</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>20665</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>1,87%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>1,14%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>2,95%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>23</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>14721</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>9523</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>21824</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>2,21%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>1,43%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>3,28%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>13568</t>
+          <t>14659</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>7886</t>
+          <t>9434</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>21745</t>
+          <t>22381</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2732,32 +2732,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>28290</t>
+          <t>27785</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>20271</t>
+          <t>19773</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>38237</t>
+          <t>37784</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,84%</t>
         </is>
       </c>
     </row>
@@ -2770,72 +2770,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>897</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>645425</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>630717</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>657163</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>92,09%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>90,0%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>93,77%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>865</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>618068</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>606801</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>628324</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>92,9%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>91,2%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>94,44%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>897</t>
-        </is>
-      </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>702869</t>
+          <t>582184</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>689239</t>
+          <t>569808</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>716087</t>
+          <t>592488</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>92,24%</t>
+          <t>92,58%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>90,45%</t>
+          <t>90,61%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>93,98%</t>
+          <t>94,22%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2845,32 +2845,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>1320937</t>
+          <t>1227609</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1301380</t>
+          <t>1209389</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1337289</t>
+          <t>1243691</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>92,55%</t>
+          <t>92,32%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>91,18%</t>
+          <t>90,95%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>93,69%</t>
+          <t>93,53%</t>
         </is>
       </c>
     </row>
@@ -2883,57 +2883,57 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>977</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>700829</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>700829</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>700829</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>942</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>665340</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>665340</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>665340</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>977</t>
-        </is>
-      </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>761972</t>
+          <t>628833</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>761972</t>
+          <t>628833</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>761972</t>
+          <t>628833</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2958,17 +2958,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1427312</t>
+          <t>1329662</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1427312</t>
+          <t>1329662</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1427312</t>
+          <t>1329662</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
